--- a/docs/company_profiles_in_db.xlsx
+++ b/docs/company_profiles_in_db.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1512"/>
+  <dimension ref="A1:B2072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1559,7 +1559,6 @@
         </is>
       </c>
     </row>
-    <row r="101"/>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
@@ -2695,7 +2694,6 @@
         </is>
       </c>
     </row>
-    <row r="202"/>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
@@ -3831,7 +3829,6 @@
         </is>
       </c>
     </row>
-    <row r="303"/>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
@@ -4967,7 +4964,6 @@
         </is>
       </c>
     </row>
-    <row r="404"/>
     <row r="405">
       <c r="A405" s="1" t="inlineStr">
         <is>
@@ -6103,7 +6099,6 @@
         </is>
       </c>
     </row>
-    <row r="505"/>
     <row r="506">
       <c r="A506" s="1" t="inlineStr">
         <is>
@@ -7239,7 +7234,6 @@
         </is>
       </c>
     </row>
-    <row r="606"/>
     <row r="607">
       <c r="A607" s="1" t="inlineStr">
         <is>
@@ -8375,7 +8369,6 @@
         </is>
       </c>
     </row>
-    <row r="707"/>
     <row r="708">
       <c r="A708" s="1" t="inlineStr">
         <is>
@@ -9511,7 +9504,6 @@
         </is>
       </c>
     </row>
-    <row r="808"/>
     <row r="809">
       <c r="A809" s="1" t="inlineStr">
         <is>
@@ -10647,7 +10639,6 @@
         </is>
       </c>
     </row>
-    <row r="909"/>
     <row r="910">
       <c r="A910" s="1" t="inlineStr">
         <is>
@@ -11783,7 +11774,6 @@
         </is>
       </c>
     </row>
-    <row r="1010"/>
     <row r="1011">
       <c r="A1011" s="1" t="inlineStr">
         <is>
@@ -12919,7 +12909,6 @@
         </is>
       </c>
     </row>
-    <row r="1111"/>
     <row r="1112">
       <c r="A1112" s="1" t="inlineStr">
         <is>
@@ -14055,7 +14044,6 @@
         </is>
       </c>
     </row>
-    <row r="1212"/>
     <row r="1213">
       <c r="A1213" s="1" t="inlineStr">
         <is>
@@ -15167,7 +15155,6 @@
         </is>
       </c>
     </row>
-    <row r="1311"/>
     <row r="1312">
       <c r="A1312" s="1" t="inlineStr">
         <is>
@@ -16291,7 +16278,6 @@
         </is>
       </c>
     </row>
-    <row r="1411"/>
     <row r="1412">
       <c r="A1412" s="1" t="inlineStr">
         <is>
@@ -17427,7 +17413,5636 @@
         </is>
       </c>
     </row>
-    <row r="1512"/>
+    <row r="1513">
+      <c r="A1513" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MORGAN STANLEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPANY OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>https://www.morganstanley.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Financial Services — Investment Banking, Wealth Management, Investment Management, Institutional Securities (Sales &amp; Trading, Research)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>New York, NY; major secondary hubs: Purchase, NY (Wealth Management), Baltimore, MD (Technology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>Public (NYSE: MS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>Revenue (est.)</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>~$61.8B net revenue (FY2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>Headcount (est.)</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>~80,000 (end of 2024; stable to slightly growing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXECUTIVE LEADERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>Executive 1 — Name</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>Ted Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>Executive 1 — Title</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>Executive 1 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>Executive 2 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>Executive 2 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>Executive 2 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>Executive 3 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>Executive 3 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>Executive 3 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>Executive 4 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>Executive 4 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>Executive 4 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>Executive 5 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>Executive 5 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>Executive 5 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CULTURE &amp; VALUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Company Says)</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>Morgan Stanley frames its culture around four core values — "Do the Right Thing, Put Clients First, Lead with Exceptional Ideas, Commit to Diversity and Inclusion" — and positions itself as an "integrated firm" where Institutional Securities, Wealth Management, and Investment Management operate synergistically. Under CEO Ted Pick, the firm has emphasized a "performance-oriented culture" with "accountability at every level," signaling a firmer tone on meritocracy and execution. The company heavily promotes its diversity initiatives (Inclusive Ventures Lab, Multicultural Innovation Lab), sustainable investing through the Institute for Sustainable Investing, and increasingly positions its technology and AI investments as core to firm identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Employees Say)</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>Employee sentiment is notably bifurcated by division. Wealth Management employees praise the "strong brand name" and "excellent client platform" but complain about "bureaucratic layers," "constant metric pressure," and a culture that can feel "sales-floor aggressive" in certain Financial Advisor channels. IB analysts and associates describe a culture that is "better than Goldman on hours but not by much" and "middle of the pack on lifestyle" among bulge brackets. Technology employees in Baltimore and Purchase describe Morgan Stanley as "a bank that's trying to be a tech company but hasn't fully committed," citing "legacy systems," "approval chains for everything," and compensation that "can't compete with FAANG." Positive themes across divisions include "strong training programs," "excellent benefits," and the perception that Morgan Stanley is "classier" or "more collegial" than competitors — "white shoe culture" appears frequently as a positive. On TheLayoff.com, threads from 2024–2025 reflect anxiety about offshoring to Budapest and Mumbai, with employees noting "everything that can be moved to India is being moved." Senior-level employees (VP+) generally rate the culture more favorably, noting "good access to leadership" and "strong deal flow."</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>Core Values</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>Do the Right Thing, Put Clients First, Lead with Exceptional Ideas, Commit to Diversity and Inclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>Work Environment</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>Hybrid, generally 4 days in-office as of 2024–2025 for most roles; enforcement is firm-wide but strictness varies by division — IB and Markets are essentially 5 days, Technology in Baltimore has some flexibility with manager approval, and remote-only roles are rare and limited to specific tech/compliance functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>Pace</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>varies by division</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>Empathy (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>Creative Drive (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>Adaptability (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>Futuristic (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>Harmony (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>Data Orientation (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPENSATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>New Grad SWE Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>Mid-Level Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>Senior Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>Base Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>Equity Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>Levels</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>Analyst → Associate → Vice President → Executive Director → Managing Director</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>Front-office IB/S&amp;T summer analyst compensation matches bulge bracket "street" rate (~$110K annualized base prorated). Technology compensation is described by employees as unable to compete with FAANG. Wealth Management branch-level compensation is described as "feast or famine" for junior Financial Advisors. Compensation is generally competitive within financial services but below top tech firms for engineering roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERVIEW PROCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>Very High (IB/Markets/Quant); Moderate to High (Corporate/Risk); Moderate (Retail/Branch) — varies significantly by track</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>Process Overview</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>The process typically follows Online Application → HireVue video interview or coding assessment → Phone/Video screen → Superday final rounds (3–5 back-to-back interviews); for campus recruiting, the cycle runs from application in summer through Superdays in fall/winter, while lateral hires typically complete the process in 4–10 weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>Coding Focus</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>Technology roles use HackerRank-style assessments (2–3 problems, 60–90 minutes) testing data structures and algorithms in Java/Python/C++ at LeetCode medium difficulty; Quant/Strats roles test probability, statistics, and logic puzzles; IB and non-tech roles have no coding component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>System Design (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>Behavioral</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>SOAR (Situation, Obstacle, Action, Result) is strongly recommended for front-office roles as it maps to the firm's performance-oriented culture and emphasis on resilience under pressure; STAR is acceptable for technology and corporate roles. Behavioral is weighted approximately 40–50% in IB Superdays and higher in Wealth Management/corporate functions. Key themes assessed: leadership under pressure, teamwork, failure and recovery, motivation for Morgan Stanley specifically, and "would I want to work with this person at 2am?" factor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>Avg Rounds</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>2–6 months (campus IB cycle); 4–10 weeks (experienced lateral hires); 4–8 weeks (technology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>The summer internship is the primary pipeline for full-time analyst hiring with ~80–90% conversion rates for strong performers; for IB, networking with bankers at target school events and attending Morgan Stanley info sessions (which are tracked) is near-mandatory; referrals are highly impactful especially for lateral hires — a "warm referral" where an employee actively advocates to the hiring manager is significantly more effective than a portal-submitted referral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REMOTE / HYBRID POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>Hybrid (4 days in office)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>Remote Friendly</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>Generally 4 days in-office required firm-wide as of 2024–2025, shifted from 3 days previously. IB and Markets divisions are effectively 5 days in-office. Technology in Baltimore reportedly allows some flexibility to 3 days with manager approval. Revenue-producing roles have less flexibility. Remote-only roles are rare and limited to specific technology and compliance functions. No widespread reports of formal disciplinary actions for non-compliance, but enforcement is firm and culturally expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GLASSDOOR / EMPLOYEE RATINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>Overall Rating (/ 5.0)</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>CEO Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>Recommend to Friend</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>Work-Life Balance</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>Compensation Score</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>Culture Score</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>Key Positives</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>Strong brand name and prestige, excellent training programs, strong benefits, collegial "white shoe" culture relative to peers, good deal flow and client platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>Key Negatives</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>Long hours in front-office roles, bureaucratic layers and approval chains, offshoring concerns for operations and middle office roles, below-market tech compensation vs. FAANG, unrealistic sales targets in WM branches</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>Glassdoor aggregate, ~18,000+ reviews, 2024–2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECENT NEWS &amp; CONTROVERSIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>Controversy Level</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>Key Topics</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Offshoring to India/Budapest, RTO policy tightening, CEO transition, record revenue performance, AI deployment for financial advisors</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>Recent News</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>2024 Jan: Ted Pick became CEO succeeding James Gorman who led the firm's transformation since 2010. | 2024 Throughout: Continued offshoring of operations and technology roles to Budapest and Mumbai, generating employee anxiety on TheLayoff.com. | 2025 Jan: Morgan Stanley reported record FY2024 net revenues of $61.8B and net income of $13.4B, driven by strong performance across all three business segments. | 2024 Mid: Firm tightened hybrid work policy to generally 4 days in-office from prior 3 days for most roles. | 2023–2024: Expanded deployment of GPT-4-powered "AI @ Morgan Stanley Assistant" tool for financial advisors, one of the most prominent Wall Street AI implementations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECRUITING &amp; CONTACTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>Key Programs</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>Investment Banking Summer Analyst, Sales &amp; Trading Summer Analyst, Technology Summer Analyst, Quantitative Finance Summer Analyst, Wealth Management Summer Analyst, Investment Management Summer Analyst, MBA Summer Associate, Early Insights (Freshman/Sophomore), Richard B. Fisher Scholars</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>University Recruiting URL</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>https://www.morganstanley.com/people-opportunities/students-graduates</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>General Jobs URL</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>https://www.morganstanley.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>LinkedIn Search Tip</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>Search LinkedIn for "Morgan Stanley" + "Campus Recruiter" or "University Relations" filtered by location matching your target office; alumni from your school currently at MS in your target division are often the most effective networking contacts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>Recruiter Tip</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>For IB roles, begin networking with Morgan Stanley bankers at target school events as early as freshman year — the firm tracks info session attendance and early engagement matters. Apply as early as possible when applications open as Morgan Stanley uses rolling review for many programs. Diversity candidates should apply to Early Insights and Richard B. Fisher Scholars programs as freshmen/sophomores to enter the pipeline early and gain preferential access to summer analyst recruiting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TECH STACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>Data / ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>DevTools / CI/CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>Notable OSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>Primary Languages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERNSHIP PROGRAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>Program Exists (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>Program Name</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>Investment Banking Summer Analyst, Sales &amp; Trading Summer Analyst, Equity Research Summer Analyst, Wealth Management Summer Analyst, Investment Management Summer Analyst, Technology Summer Analyst, Quantitative Finance Summer Analyst, MBA Summer Associate, Early Insights (Freshman/Sophomore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>Duration (weeks)</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>Roles Available</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>Investment Banking, Sales &amp; Trading, Equity Research, Wealth Management, Investment Management, Technology/Engineering, Quantitative Finance/Strats, Risk, Compliance, Finance, Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>Weekly Comp (USD)</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>~$2,080–$2,200/wk front-office IB/S&amp;T/Research (~$52–$55/hr); ~$1,400–$1,800/wk Wealth Management/corporate (~$35–$45/hr); ~$1,800–$2,200/wk Technology (~$45–$55/hr, NYC high end, Baltimore lower); ~$2,200–$2,600/wk Quant/Strats (~$55–$65/hr); ~$3,000–$3,400/wk MBA Summer Associate (~$75–$85/hr prorated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>Return Offer Rate</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>~80–90% for IB summer analysts; ~75–85% for Technology and Wealth Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>Pipeline to Full-Time</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>The summer internship is explicitly the primary pipeline for full-time analyst hiring at Morgan Stanley, with the vast majority of full-time analyst offers extended to converted interns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>Application Timeline</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>IB/S&amp;T/Research: Applications open mid-to-late May for the following summer, with campus recruiting September–January and offers as early as September–October; WM/IM/Corporate: Applications open June–August, interviews September–February; Technology: Applications open July–August, interviews September–March with rolling offers; MBA Summer Associate: OCR-driven, applications September–October.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>Intern Headcount Est.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>Morgan Stanley generally does NOT provide a housing stipend for NYC summer analysts (unlike some tech firms); some relocation assistance may be available for interns placed outside their school region but this varies by year. No publicly stated GPA minimum but practical floors are 3.5+ for IB/S&amp;T at target schools, 3.7+ at non-target schools, 3.3+ for WM/Corporate/Technology. Applying to more than 2–3 divisions is discouraged as recruiters can see multiple applications. Visa sponsorship (H-1B, J-1) is available; CPT required for international students. Diversity pipeline programs (Early Insights, Richard B. Fisher Scholars) for freshmen and sophomores provide early access to summer analyst recruiting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WORKFORCE SIGNALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>WARN Activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>WARN Risk Level</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>WARN Analyst Note</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>Morgan Stanley reported record FY2024 revenue of $61.8B and net income of $13.4B with stable-to-growing headcount (~80,000), suggesting no broad workforce reduction risk. However, targeted offshoring of operations and middle-office roles to Budapest and Mumbai is an ongoing structural trend that candidates in those functions should monitor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>Reddit / Glassdoor Themes</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>The most recurring specific themes are: (1) anxiety about offshoring — employees on TheLayoff.com and Reddit repeatedly cite that "everything that can be moved to India is being moved," particularly in operations and middle office; (2) division-dependent experience — IB and WM employees describe fundamentally different cultures, with WM branch roles receiving notably lower satisfaction scores for management and work-life balance; (3) technology compensation gap — tech employees on Blind consistently describe Morgan Stanley as paying below FAANG and express frustration with legacy systems and slow approval processes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>LinkedIn Signals</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>Headcount stable to slightly growing (~80,000 end of 2024 vs. ~78,000 end of 2023). Targeted hiring visible in Wealth Management (financial advisor recruiting) and Technology (AI, data engineering, cloud migration roles). Managing Director and senior leadership turnover appears normal following the CEO transition. No signs of hiring freezes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>News / Press Signals</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>Record revenue and earnings reported for FY2024 with strong performance across all three business segments. CEO transition from James Gorman to Ted Pick in January 2024 was orderly and well-received by markets. Continued offshoring of operations and technology roles to lower-cost centers (Budapest, Mumbai) reported throughout 2024–2025. AI deployment for financial advisors received significant positive press coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>Overall Workforce Risk</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>Signal Confidence</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>Analyst Summary</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Morgan Stanley is in strong financial health with record FY2024 revenue ($61.8B) and net income ($13.4B), supporting a stable-to-growing workforce of ~80,000. Workforce risk is structurally driven (offshoring of operations/middle office) rather than distress-driven. Front-office roles (IB, S&amp;T, Wealth Management advisors), technology (especially AI, data, cloud), and client-facing positions are safe and growing; operations, middle-office, and back-office roles in high-cost locations face ongoing offshoring risk. The internship and entry-level outlook is positive — the firm continues to recruit aggressively on campus and conversion rates remain strong, making Morgan Stanley a reliable target for new graduates seeking bulge bracket finance careers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624"/>
+    <row r="1625">
+      <c r="A1625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CITIGROUP INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPANY OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Citigroup Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>https://www.citigroup.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>Financial Services / Banking — sub-sectors: Treasury &amp; Trade Solutions, Securities Services, Fixed Income, Equities, Investment Banking, Corporate Lending, US Personal Banking (Branded Cards, Retail Banking), Wealth Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>New York, NY; major secondary hubs: Jacksonville FL, Tampa FL, Irving TX, London UK, Singapore</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Public (NYSE: C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>Revenue (est.)</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>~$81.1B net revenue (FY2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>Headcount (est.)</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>~229,000 (Q4 2024; declining — targeting ~20,000 reduction over medium term)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXECUTIVE LEADERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>Executive 1 — Name</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>Jane Fraser</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>Executive 1 — Title</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>Executive 1 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>Executive 2 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>Executive 2 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>Executive 2 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>Executive 3 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>Executive 3 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>Executive 3 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>Executive 4 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>Executive 4 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>Executive 4 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>Executive 5 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>Executive 5 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>Executive 5 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CULTURE &amp; VALUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Company Says)</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>Citi positions itself as "the world's most global bank," emphasizing its unparalleled geographic footprint across approximately 160 countries and its role as a critical enabler of cross-border commerce. CEO Jane Fraser frames the current era as Citi's most significant organizational transformation in decades — a once-in-a-generation opportunity to "shape the future of banking." The company markets four Leadership Principles (We take ownership, We deliver with pride, We succeed together, We act with integrity), highlights its position as the first major US bank to disclose adjusted pay gap data, and promotes its $12B+ annual technology investment as evidence of a "tech company with a banking license."</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Employees Say)</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Employees consistently praise Citi's genuine diversity — "Citi is the most diverse big bank, period" — and the global exposure ("You will work with people in 10 countries before lunch"). Treasury &amp; Trade Solutions and Securities Services employees frequently praise intellectual depth and franchise strength. However, the dominant negatives are severe: bureaucracy and legacy systems ("Everything takes 10x longer than it should"), constant reorgs and "restructuring fatigue" under the Fraser transformation, and compensation that runs 10-20% below JPMorgan and Goldman Sachs for comparable roles. On Blind and TheLayoff.com, morale discussions frequently reference layoff anxiety with phrases like "death by a thousand cuts." Middle management is criticized as "territorial," "risk-averse," and "more focused on self-preservation than developing talent." Work-life balance varies enormously — TTS and corporate roles are praised for reasonable hours, while IBD is described as equally brutal as peers but with worse pay. Senior leadership's strategic vision is generally respected, but execution is widely seen as slow and painful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>Core Values</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>We take ownership, We deliver with pride, We succeed together, We act with integrity</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>Work Environment</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>Hybrid model requiring 3 days in-office per week (typically Tuesday-Thursday); enforcement has tightened in 2024-2025 with badge-swipe tracking confirmed in employee reviews. Trading, branch, and operations roles require full-time in-office; fully remote roles are rare and typically grandfathered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>Pace</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>varies by division</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>Empathy (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>Creative Drive (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>Adaptability (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>Futuristic (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>Harmony (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>Data Orientation (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPENSATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>New Grad SWE Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>Mid-Level Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>Senior Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>Base Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>Equity Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>Citi is widely reported to pay 10-20% below JPMorgan and Goldman Sachs for comparable roles across IB, Markets, and Technology. Front-office IB analyst compensation matches "street rate" for base salary but total comp (bonus) may lag top-paying peers. Employee reviews consistently cite compensation as a pain point relative to competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERVIEW PROCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>Moderate to High — varies by track (Retail: Moderate; Corporate: Moderate; IB/Markets: High; Quant: Very High)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>Process Overview</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>Most tracks follow a three-stage process: online application with resume/transcript submission, asynchronous HireVue video interview (3-5 behavioral questions, some tech roles add a coding assessment), and final Superday with 3-5 back-to-back interviews mixing behavioral and technical content. Experienced lateral hires follow a similar but often condensed process with more emphasis on domain expertise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>Coding Focus</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>Technology roles include HackerRank-style online assessments (2-3 problems, LeetCode easy-medium difficulty, 60-90 minutes) in Python or Java focusing on arrays, hashmaps, strings, and basic dynamic programming. Quant roles require Python/R/C++ with stochastic calculus and statistical modeling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>System Design (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>Behavioral</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>SOAR framework recommended (Situation, Obstacle, Action, Result) — particularly effective given Citi's transformation narrative. Behavioral is heavily weighted across all tracks (1-2 dedicated behavioral interviews even on IB Superdays). Key themes: resilience, adaptability to change, cross-cultural collaboration, leadership under ambiguity, and genuine motivation for Citi specifically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>Avg Rounds</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>2-4 weeks (retail/branch); 4-8 weeks (corporate/technology); 2-5 months (IB/Markets campus cycle); 4-12 weeks (experienced lateral)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>Having an internal employee referral significantly increases odds of advancing past the HireVue stage — multiple sources confirm referrals move resumes to the top of the pile. System design interviews apply to senior technology roles (C11+) only; entry-level analyst tech roles focus on coding and algorithms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REMOTE / HYBRID POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>Hybrid (3 days in office, typically Tuesday-Thursday)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>Remote Friendly</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>Badge-swipe tracking is actively enforced as of 2024-2025. Trading, branch, and operations roles require full-time in-office presence. Fully remote roles are rare and typically grandfathered or limited to specific technology functions. Key required office locations include NYC, Jacksonville FL, Tampa FL, Irving TX, Warren NJ, London, and Singapore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GLASSDOOR / EMPLOYEE RATINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>Overall Rating (/ 5.0)</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>CEO Approval</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>Recommend to Friend</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>Work-Life Balance</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>Compensation Score</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>Culture Score</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>Key Positives</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>Genuine diversity and inclusion, global exposure and cross-border work, strong benefits and PTO, intellectual depth in TTS and Services franchises, reasonable work-life balance in corporate functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>Key Negatives</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>Bureaucracy and legacy systems, constant reorgs and restructuring fatigue, below-market compensation vs. JPM/GS, weak middle management, layoff anxiety</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>Glassdoor aggregate, 42,000+ reviews, 2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECENT NEWS &amp; CONTROVERSIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>Controversy Level</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>Key Topics</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>Organizational restructuring and mass layoffs, OCC/Fed consent order remediation, regulatory scrutiny on risk and controls infrastructure, below-peer financial performance historically</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>Recent News</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>2024 Jan: Citi announced plans to cut approximately 20,000 jobs over the medium term as part of CEO Jane Fraser's organizational simplification, the largest restructuring in decades. | 2024 Q1-Q4: Ongoing layoffs executed in waves across multiple divisions and geographies as part of the simplification plan, eliminating management layers and reducing headcount from ~240,000 to ~229,000. | 2024 FY: Citi continued remediation of the 2020 OCC/Fed consent order related to risk management, data governance, and internal controls deficiencies; regulatory scrutiny remains active. | 2025 Apr: Q1 2025 earnings reported $21.6B revenue (+3% YoY), showing continued progress on transformation and improved profitability with net income of $12.7B for FY2024. | 2024: Citi completed or advanced exits from consumer banking operations in multiple international markets as part of strategic simplification to focus on institutional and wealth businesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECRUITING &amp; CONTACTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>Key Programs</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>Investment Banking Summer Analyst, Markets Summer Analyst, Treasury &amp; Trade Solutions Summer Analyst, Technology Summer Analyst, Quantitative Analysis Summer Analyst, Wealth Management Summer Analyst, Risk Management Summer Analyst, Operations &amp; Technology Summer Analyst, Early ID / Early Insights Programs, MBA Summer Associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>University Recruiting URL</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>https://jobs.citi.com/campus</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>General Jobs URL</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>https://jobs.citi.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>LinkedIn Search Tip</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>Search LinkedIn for "Citi Campus Recruiting" or "Citi University Relations" to find dedicated campus recruiters; also search for recent Citi Analysts from your school who can serve as referral contacts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>Recruiter Tip</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>Apply within the first week of applications opening — Citi uses rolling review and spots fill quickly, especially for IB. Networking with Citi campus ambassadors and attending virtual info sessions BEFORE applying is strongly recommended, as having a contact flag your application meaningfully increases advancement odds. For non-target school candidates, a referral from any Citi employee (even in a different division) significantly improves chances of receiving a HireVue invitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TECH STACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>Data / ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>DevTools / CI/CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>Notable OSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>Primary Languages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERNSHIP PROGRAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>Program Exists (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>Program Name</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>Investment Banking Summer Analyst, Markets Summer Analyst, Treasury &amp; Trade Solutions Summer Analyst, Technology Summer Analyst, Quantitative Analysis Summer Analyst, Wealth Management Summer Analyst, Risk Management Summer Analyst, Operations &amp; Technology Summer Analyst, Early ID / Early Insights Programs, MBA Summer Associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>Duration (weeks)</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>Roles Available</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>Investment Banking, Markets (FICC, Equities), Treasury &amp; Trade Solutions, Securities Services, Technology, Quantitative Analysis, Wealth Management, Risk Management, Operations, Finance, Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>Weekly Comp (USD)</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>~$1,900–$2,100/wk (front-office IB/Markets, based on ~$110K annualized street rate for 2024); ~$1,500–$1,800/wk (Technology); ~$1,200–$1,500/wk (corporate functions: TTS, Risk, Wealth); ~$1,000–$1,200/wk (Operations-track) (unverified for some corporate/ops tiers — derived from hourly rates in Step 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>Return Offer Rate</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>~70-85% for IB and Markets; ~70%+ for Technology; ~60-75% for corporate functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>Pipeline to Full-Time</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>The summer internship is the primary pipeline for full-time Analyst and Associate hiring — a large majority of full-time offers (especially in IB) come from converting summer interns, making external full-time applications highly competitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>Application Timeline</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>IB/Markets/front-office: late June-July (for following summer); Technology: August-September; Corporate functions: September-November; MBA: August-October; Early ID/Freshman programs: January-March</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>Intern Headcount Est.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>Housing stipend of approximately $2,500-$3,500/month reported for NYC interns (verify during offer process). Applicants may generally apply to 1-2 programs per recruiting cycle (one first-choice, one second-choice division — check portal for current limits). Effective GPA thresholds: IB/Markets 3.5+, Technology 3.3+, Corporate 3.0+. Citi sponsors H-1B and J-1 visas for interns. Separate early deadlines may exist for diversity-focused pipeline programs. IB offers may be extended by October-November, so applications should be submitted by August-September at the latest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WORKFORCE SIGNALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>WARN Activity</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>Citi announced plans in January 2024 to cut approximately 20,000 jobs over the medium term as part of CEO Fraser's organizational simplification. Layoffs have been executed in waves throughout 2024 and into 2025 across multiple divisions and geographies. Specific WARN Act filings have been associated with these reductions in various states, consistent with the announced restructuring strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>WARN Risk Level</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>WARN Analyst Note</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>The ~20,000 headcount reduction is structural and transformation-driven, not a response to acute financial distress. However, candidates should be aware that layoffs are ongoing and expected to continue through 2025-2026, particularly in middle management, overlapping operations, and functions being simplified or consolidated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>Reddit / Glassdoor Themes</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>Restructuring fatigue and layoff anxiety dominate employee sentiment — "death by a thousand cuts" is a recurring phrase on Blind and TheLayoff.com. Employees describe not knowing if their role will exist next quarter. Below-market compensation relative to JPM and Goldman is the second most consistent complaint, and bureaucracy/legacy systems creating operational friction is the third.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>LinkedIn Signals</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>Overall headcount trending downward from ~240,000 to ~229,000 (YE2023 to YE2024) with further reductions expected. However, selective hiring continues in priority areas including technology transformation, regulatory/compliance remediation, and revenue-generating front-office roles in TTS, Markets, and Banking. LinkedIn job postings remain active in these targeted growth areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>News / Press Signals</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>Extensive press coverage throughout 2024-2025 of the organizational simplification and associated layoffs, described as the largest restructuring in Citi's modern history. Coverage also highlights ongoing OCC/Fed consent order remediation and Citi's strategic exits from international consumer banking markets. Q1 2025 earnings coverage noted improved financial performance and continued transformation progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>Overall Workforce Risk</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>Signal Confidence</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>Analyst Summary</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>Citi is financially stable (FY2024 net income of ~$12.7B, improved revenues) but is in the midst of a multi-year structural transformation that involves eliminating ~20,000 positions, primarily in middle management, duplicative operations, and functions being simplified. This is strategic, not distress-driven, but creates elevated risk for candidates joining non-priority areas. Revenue-generating front-office roles (IB, Markets, TTS), technology transformation positions, and regulatory/compliance remediation roles are relatively safe and actively hiring. Internship and entry-level analyst programs remain robust with strong conversion rates, as Citi continues to invest in its junior talent pipeline even during the restructuring — these programs are among the safest entry points during this period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736"/>
+    <row r="1737">
+      <c r="A1737" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BANK OF AMERICA CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPANY OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>https://www.bankofamerica.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>Financial Services / Banking — Consumer Banking, Wealth Management, Global Banking (Corporate &amp; Investment Banking), Global Markets (Sales &amp; Trading, Research)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>Charlotte, NC; major secondary hubs: New York, NY and Jacksonville, FL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>Public (NYSE: BAC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>Revenue (est.)</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>~$101.9B net revenue (FY2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>Headcount (est.)</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>~213,000 (December 2024; stable to slightly declining)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXECUTIVE LEADERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>Executive 1 — Name</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>Brian Moynihan</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>Executive 1 — Title</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>Chairman and Chief Executive Officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>Executive 1 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>Executive 2 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>Executive 2 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>Executive 2 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>Executive 3 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>Executive 3 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>Executive 3 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>Executive 4 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>Executive 4 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>Executive 4 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>Executive 5 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>Executive 5 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>Executive 5 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CULTURE &amp; VALUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Company Says)</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>Bank of America positions itself as driven by "responsible growth" — growing sustainably while serving all stakeholders. The company brands itself as "a great place to work for all," emphasizing four pillars: being a great place to work, being trusted by clients, delivering for shareholders, and growing responsibly in communities. BAC highlights its commitment to DEI, its internal "Academy" career development program, tuition reimbursement, a minimum wage path to $25/hour by 2025, and a "speak-up" culture reflecting its post-2008 cultural transformation under CEO Moynihan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Employees Say)</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>Positive themes include genuinely best-in-class benefits (401k match, parental leave, tuition reimbursement), decent work-life balance in corporate and operations roles, and diversity initiatives perceived as authentic rather than performative. Negative themes are substantial and consistent: excessive bureaucracy with too many approval layers and slow decision-making, described as "good ideas die in committee." IB division is described on Wall Street Oasis as having "brutal hours comparable to other bulge brackets but with less exit opportunity prestige than Goldman or JPM." Retail/branch employees report high cross-sell pressure — "it's all about the numbers, you're just a sales machine." Technology employees on Blind note comp lags 30-40% behind big tech and even behind JPMorgan's tech arm, with legacy-heavy tech stacks. Sentiment varies dramatically by manager quality — "your experience depends entirely on your manager" appears almost verbatim across hundreds of reviews. Senior Management is consistently the weakest-rated dimension on Glassdoor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>Core Values</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>Responsible Growth, Deliver Together, Act Responsibly, Realize the Power of Our People, Trust the Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>Work Environment</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>Hybrid, minimum 3 days in-office per week (Tuesday-Thursday typical anchor schedule); enforcement has tightened through 2024 with badge-swipe monitoring reportedly used. IB/Markets roles are effectively 4-5 days in-office; fully remote roles are rare. Key offices: Charlotte, NYC (One Bryant Park), Jacksonville, Pennington, Dallas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>Pace</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>varies by division</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>Empathy (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>Creative Drive (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>Adaptability (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>Futuristic (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>Harmony (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>Data Orientation (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPENSATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>New Grad SWE Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>Mid-Level Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>Senior Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>Base Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>Equity Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>Technology compensation reported as 30-40% below big tech (FAANG) and below JPMorgan Chase tech roles per Blind. Front-office IB/Markets analyst compensation is in line with bulge bracket peers at ~$110K annualized for summer analysts. Minimum wage raised to $24/hour in 2024, on path to $25/hour by 2025. Notable perks include 401(k) match, tuition reimbursement, parental leave, and sabbatical programs for long-tenured employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERVIEW PROCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>Moderate to High — varies by track (Retail: Low-Medium; Corporate: Medium-High; IB/Markets: High; Quant: High)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>Process Overview</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>The process typically consists of an online application, a HireVue on-demand video interview (behavioral/motivational for IB, coding assessment for tech), an optional phone screen, and a final Superday with 3-5 back-to-back interviews mixing behavioral (60%) and technical (40%) questions. Technology roles substitute a live coding interview and hiring manager round for the Superday format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>Coding Focus</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>Technology roles include a HackerRank/Codility online assessment (2-3 problems, 60-90 minutes, LeetCode medium difficulty) and a live coding interview focusing on data structures, algorithms, and SQL. Languages: Java, Python. N/A for non-tech tracks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>System Design (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>Behavioral</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>SOAR framework recommended (Situation, Obstacle, Action, Result) — aligns with BofA's post-2008 transformation narrative and emphasis on risk awareness. Behavioral questions weighted ~60% of IB/Markets interviews. Key themes: leadership, teamwork, failure/learning, conflict resolution, initiative, analytical problem-solving. Prepare 6-8 specific stories with quantified results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>Avg Rounds</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>2-4 weeks (retail/branch); 4-8 weeks (corporate/technology); 6-12 weeks (IB/Markets lateral)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>For IB, know 2-3 recent BofA-specific deals and have a crisp "Why BofA over JPM/GS/MS?" answer — interviewers hear this daily. Apply as early as possible as rolling admission is the practical reality; IB applications submitted after October are at significant disadvantage. Campus event attendance is tracked and shared with recruiters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REMOTE / HYBRID POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>Hybrid (3 days in office minimum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>Remote Friendly</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>Most corporate employees required in-office minimum 3 days per week (Tuesday-Thursday anchor). IB/Markets effectively 4-5 days in-office. Badge-swipe monitoring reportedly used to enforce attendance as of 2024. Fully remote roles are rare and limited to specific tech or specialized positions. Branch/retail roles are fully on-site. Key required office locations: Charlotte, NYC, Jacksonville, Pennington, Dallas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GLASSDOOR / EMPLOYEE RATINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>Overall Rating (/ 5.0)</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>CEO Approval</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>~80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>Recommend to Friend</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>~73%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>Work-Life Balance</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>Compensation Score</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>Culture Score</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>Key Positives</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>Best-in-class benefits (401k, parental leave, tuition reimbursement), decent work-life balance in corporate roles, authentic DEI programs, strong job stability, good PTO and sabbatical programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>Key Negatives</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>Excessive bureaucracy and slow decision-making, weak senior management ratings, high pressure and metrics-driven branch culture, below-market tech compensation, experience depends entirely on manager quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>Glassdoor aggregate, ~68,000+ reviews, 2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECENT NEWS &amp; CONTROVERSIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>Controversy Level</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>Key Topics</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>RTO enforcement tightening, gradual headcount reductions through attrition, legacy technology modernization challenges, post-2008 regulatory scrutiny legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>Recent News</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>2025 Jan: Q4 2024 earnings reported with FY2024 net income of ~$27.1B, representing year-over-year increase driven by NII recovery and strong trading fees. | 2025 Apr: Q1 2025 earnings call indicated continued investment in technology and financial advisors while rationalizing operations headcount. | 2024: Minimum wage raised to $24/hour with stated path to $25/hour by 2025. | 2024: Hybrid RTO enforcement tightened with badge-swipe monitoring reported by employees on Blind and Reddit. | 2024: Headcount declined from ~217,000 (end 2023) to ~213,000 (end 2024) through attrition rather than large-scale RIFs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECRUITING &amp; CONTACTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>Key Programs</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>Global Investment Banking Summer Analyst, Global Markets Summer Analyst, Global Technology Summer Analyst (GTAP), Global Wealth &amp; Investment Management Summer Analyst, Global Risk Summer Analyst, Global Finance/Corporate Functions Summer Analyst, Sophomore Summer Analyst (Diversity Focused), Global Investment Banking Summer Associate (MBA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>University Recruiting URL</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>https://campus.bankofamerica.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>General Jobs URL</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>https://careers.bankofamerica.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>LinkedIn Search Tip</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>Search LinkedIn for "Bank of America" + "Campus Recruiter" or "University Relations" filtered by the specific division (e.g., "Global Banking Recruiting") and target location to find the most relevant recruiter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>Recruiter Tip</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>Apply as early as possible — IB applications open late June to early August for the following summer, and many offers are extended by October-November. Attend all BofA-sponsored campus events (info sessions, coffee chats) as attendance is tracked and shared with recruiters. For IB, a referral from a VP+ in the specific coverage or product group is significantly more impactful than a generic referral; network aggressively at target school events in September.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TECH STACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>Data / ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>DevTools / CI/CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>Notable OSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>Primary Languages</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERNSHIP PROGRAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>Program Exists (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>Program Name</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>Global Investment Banking Summer Analyst, Global Markets Summer Analyst, Global Investment Banking Summer Associate, Global Technology Summer Analyst (GTAP), Global Wealth &amp; Investment Management Summer Analyst, Global Risk Summer Analyst, Global Finance/Corporate Functions Summer Analyst, Sophomore Summer Analyst (Diversity Focused)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>Duration (weeks)</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>Roles Available</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>Investment Banking Analyst, Sales &amp; Trading Analyst, Technology Analyst, Wealth Management Analyst, Risk Analyst, Finance/Corporate Functions Analyst, MBA Associate (IB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>Weekly Comp (USD)</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>~$2,080–$2,200/wk (IB/Markets front office, ~$52–$55/hr); ~$1,680–$2,000/wk (Technology, ~$42–$50/hr); ~$1,520–$1,800/wk (Wealth Management/Risk, ~$38–$45/hr); ~$1,400–$1,680/wk (Corporate Functions, ~$35–$42/hr); ~$2,880–$3,120/wk (MBA Associate, ~$72–$78/hr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>Return Offer Rate</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>~70-85% (IB/Markets); ~75-85% (Technology); strong across all programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>Pipeline to Full-Time</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>The internship program is the primary full-time hiring pipeline — the firm views summer analyst/associate programs as the central mechanism for filling entry-level and post-MBA roles, with non-converting external applications filling a smaller share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>Application Timeline</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>IB/Markets: late June to early August (for following summer, with offers by Oct-Nov); Technology: August-September; Corporate Functions: September-January; Sophomore Diversity Programs: August-October</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>Intern Headcount Est.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>Housing stipend not universally offered — some programs provide a relocation lump sum of $3,000-$5,000 (varies by year and location, confirm at offer stage). No strict per-cycle application limit but applying to more than 2-3 programs is discouraged as recruiters see all applications. GPA preferences: IB/Markets 3.5+ (3.7+ competitive), Technology 3.2+, Corporate Functions 3.0+. BAC sponsors H-1B and OPT/STEM OPT for interns and full-time hires in most programs. Expanded sophomore diversity pipeline programs designed to convert into junior-year summer analyst offers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WORKFORCE SIGNALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>WARN Activity</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>No large-scale WARN filings identified in recent reporting. Headcount reductions have been managed through gradual attrition and selective efficiency programs rather than mass layoffs requiring WARN notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>WARN Risk Level</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>WARN Analyst Note</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>BAC's approach of managing headcount through attrition rather than large-scale RIFs suggests disciplined workforce planning. Candidates should not expect sudden mass layoffs, though operations and back-office roles face the most rationalization pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>Reddit / Glassdoor Themes</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>Recurring themes on Reddit (r/FinancialCareers), Wall Street Oasis, and Glassdoor: (1) BofA IB is a solid bulge bracket but ranks 3rd-4th behind GS/MS/JPM for prestige and PE exit opportunities; (2) technology roles offer good WLB but significantly below-market compensation compared to big tech; (3) branch/retail roles face intense sales metric pressure described as "you're just a sales machine."</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>LinkedIn Signals</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>Headcount trending slightly downward (~217K to ~213K over 2023-2024). Continued investment in technology roles and financial advisor hiring. Operations and back-office roles are the primary areas of rationalization. Overall hiring velocity appears moderate and targeted rather than expansionary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>News / Press Signals</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>Q1 2025 earnings call signaled continued investment in technology and financial advisors while rationalizing operations headcount. FY2024 net income grew year-over-year, indicating financial health supports selective hiring. No major layoff announcements in 2024-2025; workforce reductions have been gradual and attrition-based.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>Overall Workforce Risk</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>Signal Confidence</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>Analyst Summary</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>Bank of America is financially healthy with FY2024 net income of ~$27.1B and growing revenue, providing a stable foundation for continued hiring. Workforce reductions are structural efficiency-driven (operations rationalization, automation) rather than distress-driven, and are managed through attrition. Front-office roles (IB, Markets, Wealth Management advisors) and technology positions are the safest and most actively hired; operations and back-office roles face the most headcount pressure. Internship and entry-level campus programs remain robust and are the firm's primary full-time hiring pipeline, with strong return offer rates of 70-85% across divisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848"/>
+    <row r="1849">
+      <c r="A1849" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  JPMORGAN CHASE &amp; CO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPANY OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>1799</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>https://www.jpmorganchase.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>Financial Services — Diversified Banking (Consumer &amp; Community Banking, Corporate &amp; Investment Banking, Commercial Banking, Asset &amp; Wealth Management)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>New York, NY; major secondary hubs in Columbus, OH and London, UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>Public (NYSE: JPM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>Revenue (est.)</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>~$180.6B managed net revenue (FY2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>Headcount (est.)</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>~317,233 (December 2024; growing — added ~7,300 net employees in 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXECUTIVE LEADERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>Executive 1 — Name</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>Jamie Dimon</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>Executive 1 — Title</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>Chairman and Chief Executive Officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>Executive 1 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>Executive 2 — Name</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>Daniel Pinto</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>Executive 2 — Title</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>President and Chief Operating Officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>Executive 2 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>Executive 3 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>Executive 3 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>Executive 3 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>Executive 4 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>Executive 4 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>Executive 4 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>Executive 5 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>Executive 5 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>Executive 5 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CULTURE &amp; VALUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Company Says)</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase positions itself as running "a first-class business in a first-class way," emphasizing exceptional client service, operational excellence, integrity, and a "fortress balance sheet" mentality that prizes risk discipline. The firm's employer branding heavily promotes its $17+ billion annual technology investment, positioning JPM as "a technology company with a banking license," with CEO Jamie Dimon's shareholder letters extensively discussing AI investment, embracing disruption, and the firm's ambition to be a top-tier technology employer. The company highlights over 10 Business Resource Groups and signature programs like Advancing Black Pathways and Women on the Move as evidence of structural DEI investment, stating "we don't just talk about being inclusive — we live it."</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Employees Say)</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>Positives: Employees consistently praise brand prestige and career optionality, noting that "having JPM on your resume opens doors everywhere," and that the firm's size creates unmatched internal mobility. Benefits including 401(k) match, healthcare, 16-week parental leave, and tuition reimbursement are rated above-average. Technology employees report a more modern tech stack than expected and interesting work on cloud migration and AI/ML platforms. Negatives: The most repeated complaints are bureaucracy and internal politics, with reviews using phrases like "red tape everywhere," "too many layers of approval," and "managing up matters more than doing good work." Tech total compensation lags FAANG by 20-40% at mid-to-senior levels. Significant employee backlash over the 5-day RTO mandate, described as "out of touch" and "the single biggest reason people are leaving." Operations and compliance employees report anxiety about offshoring, with reports that "entire teams in Columbus got knowledge-transferred to India." Sentiment varies significantly: AWM and Private Banking employees tend most positive; Operations/Compliance most negative; IB analysts express a love-hate relationship; Tech employees are split based on team and manager quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>Core Values</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>Exceptional client service, Operational excellence, Integrity fairness and responsibility, A commitment to our people, A culture of inclusion and respect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>Work Environment</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>5 days in-office mandate for most full-time employees as of early 2025, enforced via badge swipe tracking. Some tech roles hired during 2020-2022 retained 3-day hybrid schedules, but exceptions are limited; key locations include 270 Park Ave NYC (new HQ), Columbus OH, Jersey City NJ, London, Plano TX, and Bengaluru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>Pace</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>varies by division</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>Empathy (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>Creative Drive (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>Adaptability (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>Futuristic (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>Harmony (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>Data Orientation (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPENSATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>New Grad SWE Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>Mid-Level Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>Senior Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>Base Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>Equity Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>IB first-year analyst base approximately $110K (2024). Tech total comp lags FAANG by 20-40% at mid-to-senior levels per Blind reports. Front-office roles (IB, Markets) compensated at market rates for bulge bracket banks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERVIEW PROCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>Varies by track — Low-to-Moderate (Retail/Branch), Moderate (Corporate), High (IB/Markets), Very High (Quant), Moderate-to-High (Tech SWE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>Process Overview</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>Most tracks follow a three-to-four step process: online application, HireVue video interview (behavioral, AI-scored) or online coding assessment (for tech), followed by phone/video screen and a final Superday of 3-5 back-to-back interviews mixing behavioral and technical questions. IB and Markets full-time roles are predominantly filled through intern conversion rather than external applications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>Coding Focus</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>Tech (SWE) roles use HackerRank or similar platforms with 1-3 problems at LeetCode medium-to-hard difficulty, primarily in Java or Python, testing data structures, algorithms, and clean code. IB/Markets roles do not have coding assessments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>System Design (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>Behavioral</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>SOAR (Situation, Obstacle, Action, Result) framework recommended; behavioral carries heavy weight across all tracks, with JPM interviewers probing for resilience, problem-solving under pressure, and navigating complexity. Key themes: leadership challenge, teamwork conflict, failure/resilience, analytical problem-solving, initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>Avg Rounds</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>2-4 weeks (Retail); 4-8 weeks (Corporate/Tech); 6-12 weeks (IB/Markets campus recruiting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>IB applications operate on an effectively rolling basis — apply within the first 1-2 weeks of the window opening. A referral from a current employee significantly increases interview probability (estimated 3-5x). HireVue is AI-scored with human review; practice eye contact with camera and keep answers to 60-90 seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REMOTE / HYBRID POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>In-office 5 days (majority of roles as of early 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>Remote Friendly</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>Jamie Dimon's January 2025 memo mandated full 5-day RTO for most employees. Enforcement is high with badge swipe tracking confirmed by multiple employee reports. Limited exceptions exist for certain tech roles hired as hybrid/remote during 2020-2022 and roles in locations without sufficient office space. The mandate generated significant employee backlash across Reddit and Blind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GLASSDOOR / EMPLOYEE RATINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>Overall Rating (/ 5.0)</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>CEO Approval</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>Recommend to Friend</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>Work-Life Balance</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>Compensation Score</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>Culture Score</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>Key Positives</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>Brand prestige and resume value, strong benefits and 401(k) match, internal mobility and career optionality, interesting work on technology and AI initiatives, above-average parental leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>Key Negatives</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>Bureaucracy and excessive red tape, internal politics and managing up culture, rigid RTO enforcement, offshoring concerns in operations and compliance, work-life balance pressure in front-office roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>Glassdoor aggregate, ~32,000+ reviews, 2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECENT NEWS &amp; CONTROVERSIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>Controversy Level</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>Key Topics</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>RTO enforcement backlash, offshoring operations to India, DEI program language adjustments, First Republic Bank integration, CEO succession speculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>Recent News</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>2025 Jan: Jamie Dimon issued memo mandating 5-day in-office return for most employees, generating widespread employee backlash. | 2025 Apr: Q1 2025 earnings reported $46.0B net revenue and $14.6B net income, exceeding analyst expectations. | 2024-2025: Opened new 270 Park Avenue global headquarters, the largest all-electric skyscraper in the US. | 2024: Adjusted some DEI program language in response to broader political and legal pressures. | 2023 May: Acquired First Republic Bank out of FDIC receivership; integration continued through 2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECRUITING &amp; CONTACTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>Key Programs</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>Investment Banking Summer Analyst, Markets Summer Analyst, Software Engineering Program (SEP) Intern, Asset &amp; Wealth Management Summer Analyst, Commercial Banking Summer Analyst, Global Finance &amp; Business Management Summer Analyst, Quantitative Analytics Summer Associate, Launching Leaders Program, ACES Freshman Program</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>University Recruiting URL</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>https://careers.jpmorgan.com/us/en/students</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>General Jobs URL</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>https://careers.jpmorgan.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>LinkedIn Search Tip</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>Search LinkedIn for "JPMorgan campus recruiter" or "JPMorgan university recruiting" filtered by current company to find division-specific campus recruiters assigned to your target school or region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>Recruiter Tip</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>Apply within the first 1-2 weeks of the application window opening, as IB and Markets programs fill on a rolling basis despite stated deadlines. Attend JPM-hosted information sessions and diversity events before applying, as these create flags in the applicant tracking system. Obtain a referral from a current JPM employee through informational conversations — referrals are formally tracked and significantly increase first-round interview probability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TECH STACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>Java, Python, Spring Boot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>AWS (cloud migration partnership)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>Data / ML</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>Internal AI/ML organization (one of the largest in financial services), LLM Suite (internal tool), ~2,000+ data scientists and quantitative analysts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>DevTools / CI/CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>Notable OSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>Primary Languages</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>Java, Python, C++</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>JPM invests $17B+ annually in technology. Active cloud migration to AWS. Internal platforms include Athena/Quartz-replacement systems. Blockchain initiatives include Onyx/JPM Coin and quantum computing research. Some offshoring of tech/ops functions to Bengaluru and Mumbai reported by employees. Tech stack described by employees as "more modern than expected — not the Java-only dinosaur people assume."</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERNSHIP PROGRAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>Program Exists (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>Program Name</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>Investment Banking Summer Analyst, Markets Summer Analyst, Software Engineering Program (SEP) Intern, Asset &amp; Wealth Management Summer Analyst, Commercial Banking Summer Analyst, Global Finance &amp; Business Management Summer Analyst, Quantitative Analytics Summer Associate, MBA Summer Associate, Launching Leaders Program, ACES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>Duration (weeks)</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>Roles Available</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>Investment Banking Analyst, Sales &amp; Trading Analyst, Software Engineer, Asset &amp; Wealth Management Analyst, Commercial Banking Analyst, Finance &amp; Business Management Analyst, Quantitative Analyst, MBA Associate (IB/AWM/CB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>Weekly Comp (USD)</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>~$1,520-$1,680/wk (IB/Markets, prorated from ~$110K analyst base); ~$1,520-$2,080/wk (Tech SWE, ~$38-$52/hr varying by location); ~$1,200-$1,440/wk (Corporate/Operations, ~$30-$36/hr); ~$2,200-$2,800/wk (MBA Associate, prorated from ~$175K base)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>Return Offer Rate</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>~80-90% for IB/Markets; ~75-85% for Tech; ~70-80% for Corporate functions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>Pipeline to Full-Time</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>The internship is explicitly the primary pipeline to full-time employment — the vast majority of full-time IB, Markets, and Tech analyst offers go to returning summer interns, making the internship function as an extended interview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>Application Timeline</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>IB/Markets: late June-July (12 months ahead); Tech: August-September; Corporate: August-October; MBA Associate: September-January; Diversity pipeline programs (Launching Leaders, ACES): spring for fall participation</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>Intern Headcount Est.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>Candidates limited to approximately 3 program applications per recruiting cycle. Housing stipends of $3,000-$5,000 or corporate housing offered for relocating interns (varies by program/location). No formal published GPA minimum, but effective unwritten floors: 3.5+ for IB/Markets at target schools, 3.7+ at non-targets; 3.2+ for Tech; 3.0+ for Corporate. Diversity-focused pipeline programs include Launching Leaders and ACES freshman exposure programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WORKFORCE SIGNALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>WARN Activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>WARN Risk Level</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>WARN Analyst Note</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase grew headcount by approximately 7,300 net employees in 2024, indicating expansion rather than contraction. While offshoring of operations and compliance functions to India has been reported by employees, this represents role migration rather than mass layoffs triggering WARN filings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>Reddit / Glassdoor Themes</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>Offshoring anxiety is the most specific recurring theme, with employees on TheLayoff.com and Reddit reporting knowledge transfer of entire Columbus-based teams to India in operations and compliance functions. The 5-day RTO mandate is the second most discussed topic, with employees on Blind and Reddit describing it as a top driver of voluntary attrition. Tech employees on Blind frequently discuss the comp gap vs. FAANG as a retention risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>LinkedIn Signals</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>Net headcount growing (~317K at end of 2024, up from ~310K at end of 2023). Active hiring in technology (AI/ML, cloud, cybersecurity), new branch expansion, and Plano TX hub growth. Continued investment in early-career pipeline programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>News / Press Signals</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>First Republic Bank integration completed through 2024 with associated role consolidation. Q1 2025 earnings beat expectations with $14.6B net income. Jamie Dimon continues to signal aggressive technology and AI investment. No major layoff announcements in 2024-2025; growth posture maintained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>Overall Workforce Risk</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>Signal Confidence</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>Analyst Summary</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase is in exceptionally strong financial health as the most profitable bank globally, with FY2024 net income of $58.5B and growing headcount. Workforce risk is structural (offshoring of operations/compliance) rather than distress-driven, meaning front-office, technology, and client-facing roles remain safe and growing. Roles most at risk are middle-office operations, certain compliance functions, and back-office roles susceptible to India-based knowledge transfer. The internship and entry-level outlook is strong across all major divisions, with the firm actively expanding its campus recruiting pipeline and early-career programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960"/>
+    <row r="1961">
+      <c r="A1961" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WELLS FARGO &amp; COMPANY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPANY OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>Wells Fargo &amp; Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>1852</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>https://www.wellsfargo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>Financial Services / Banking — Consumer Banking &amp; Lending, Commercial Banking, Corporate &amp; Investment Banking (CIB), Wealth &amp; Investment Management (WIM), Auto Lending, Home Lending/Mortgage, Credit Cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>San Francisco, CA; major secondary hub in Charlotte, NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>Public (NYSE: WFC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>Revenue (est.)</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>~$82.3B total revenue (FY2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>Headcount (est.)</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>~217,000 (December 2024; declining — down from ~227K at YE2023 and ~238K at YE2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXECUTIVE LEADERSHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>Executive 1 — Name</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>Charles W. Scharf</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>Executive 1 — Title</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>Executive 1 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>Executive 2 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>Executive 2 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>Executive 2 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>Executive 3 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>Executive 3 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>Executive 3 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>Executive 4 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>Executive 4 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>Executive 4 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>Executive 5 — Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>Executive 5 — Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>Executive 5 — LinkedIn URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CULTURE &amp; VALUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Company Says)</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>Wells Fargo brands itself as a company undergoing a "cultural transformation," emphasizing accountability, transparency, and putting customers first in the wake of its 2016 fake-accounts scandal and subsequent regulatory consent orders. Under CEO Scharf, the company promotes "building the right foundation" through organizational simplification, enhanced controls, operating excellence, and risk management as cultural cornerstones. The company highlights its "Your Career. Your Way." employer brand, advertising tuition reimbursement, internal mobility, mentoring circles, and 10+ Employee Resource Networks, with a stated commitment to being "a company that is known for doing the right thing."</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>Culture Narrative (Employees Say)</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>On the positive side, employees frequently praise the generous benefits package — 401(k) match, parental leave, health insurance, and tuition reimbursement are called out as "among the best in banking," and many corporate and technology employees describe improved work-life balance and collaborative immediate teams. However, the single most repeated complaint across Glassdoor, Indeed, Blind, TheLayoff.com, and Reddit is "constant reorganization and layoffs — you never feel safe." Employees describe a culture of "fear and micromanagement" especially at the branch and operational levels, with phrases like "metrics-driven to an unhealthy degree" and "they treat you like a number." On Blind, Wells Fargo is frequently described as a "cost-cutting machine" where morale is low due to ongoing headcount reductions and offshoring. Branch/retail employees consistently report being understaffed, underpaid relative to workload, and subjected to aggressive sales goals. Technology employees in Charlotte and Chandler report improving conditions and appreciate hybrid flexibility, while branch employees and legacy operations roles report significantly worse experiences. On Wall Street Oasis, the CIB division gets mixed reviews — deal flow is "improving but still below JPM/GS/MS tier" and the bank's reputational issues make client-facing work harder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>Core Values</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>We value what's right for our customers, We act with integrity, We are inclusive, We advocate for our communities, We strive for excellence</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>Work Environment</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>Structured hybrid model requiring most corporate employees in-office 3 days per week (typically Tuesday, Wednesday, Thursday), with enforcement tightening in 2024–2025 including badge-swipe monitoring; some roles designated as full office (4–5 days) or remote (limited, primarily in technology), and branch employees are fully in-office. Major hub locations include Charlotte, San Francisco, New York, Minneapolis, Chandler, and Des Moines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>Pace</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>varies by division</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>Empathy (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>Creative Drive (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>Adaptability (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>Futuristic (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>Harmony (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>Data Orientation (0.0–1.0)</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COMPENSATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>New Grad SWE Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>Mid-Level Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>Senior Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>Base Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>Equity Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>Levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>Blind discussions suggest WFC pays below JPMorgan and Citi for comparable tech roles; CIB front-office IB analyst compensation is generally at or near street rate; compensation is considered a known pain point for technology relative to top-tier competitors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERVIEW PROCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>Difficulty</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>Moderate to High — varies by track (Low-Moderate for retail/branch, Moderate for corporate programs, High for IB/Markets and specialized tech/quant roles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>Process Overview</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>The end-to-end process typically involves an online application, HireVue video interview and/or online assessment (coding for tech, behavioral for others), a phone/video screen with a recruiter or hiring manager, and a final round consisting of 2–5 back-to-back interviews (Superday format for IB). Timeline ranges from 2–4 weeks for retail to 6–12 weeks for IB and senior technology roles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>Coding Focus</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>Technology roles require a HackerRank or similar coding assessment with 2–3 problems at easy-to-medium difficulty, testing data structures, algorithms, and basic problem-solving in Java, Python, or C++; some roles include SQL questions. LeetCode easy/medium preparation recommended with focus on arrays, strings, hash maps, and basic tree/graph traversal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>System Design (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>Behavioral</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>SOAR framework (Situation, Obstacle, Action, Result) recommended over STAR because WFC interviewers are attuned to candidates who navigate challenges and demonstrate resilience, reflecting the company's own regulatory and transformation environment. Behavioral weight is approximately 50–60% for most tracks and up to 60% for IB. Key themes: ethical decision-making, teamwork under pressure, leadership without authority, failure/recovery, and genuine motivation for Wells Fargo specifically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>Avg Rounds</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>2–4 weeks (retail); 4–8 weeks (corporate/tech); 6–12 weeks (IB/Markets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>For non-target school IB candidates, a referral from a VP+ level banker is described as essential to get past the initial screen; the bank tracks attendance at campus events and information sessions, making attendance a meaningful signal in the evaluation process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REMOTE / HYBRID POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>Hybrid (3 days in office)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>Remote Friendly</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>Most corporate employees are required in-office Tuesday, Wednesday, and Thursday. Enforcement has tightened over 2024–2025 with badge-swipe monitoring reported by employees on Blind and Reddit. Some technology roles are designated remote but availability is limited. Branch employees are fully in-office 5 days. Major required office locations include Charlotte, San Francisco, New York, Minneapolis, Chandler, Des Moines, and Dallas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GLASSDOOR / EMPLOYEE RATINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>Overall Rating (/ 5.0)</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>CEO Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>Recommend to Friend</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>Work-Life Balance</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>Compensation Score</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>Culture Score</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>Key Positives</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>Generous benefits package (401k match, parental leave, health insurance), tuition reimbursement, good for learning banking fundamentals, improved work-life balance in corporate/tech roles, active Employee Resource Networks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>Key Negatives</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>Constant reorganization and layoffs, fear-based and micromanagement culture at branch level, metrics-driven to unhealthy degree, poor senior management ratings, offshoring and headcount reduction anxiety</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>Glassdoor aggregate, ~72,000+ reviews, 2024–2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECENT NEWS &amp; CONTROVERSIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>Controversy Level</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>Key Topics</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>Fake-accounts scandal legacy, Fed asset cap (since 2018), ongoing regulatory consent orders, multi-year layoffs and headcount reduction, offshoring, RTO enforcement, reputational challenges in CIB client-facing work</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>Recent News</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>2024 Jan: Wells Fargo reported Q4 2024 earnings showing ~$18.6B net income for FY2024 with continued headcount reductions as part of efficiency initiative. | 2024 throughout: Continued multi-year headcount reduction from ~227K to ~217K employees, with CEO Scharf reiterating on earnings calls that headcount reductions remain a key lever for the efficiency program. | 2023-2024: Federal Reserve asset cap (imposed February 2018) remains in place, constraining the bank's growth; Wells Fargo has stated it continues to work toward satisfying the Fed's requirements for cap removal but no specific timeline has been given. | 2024: Wells Fargo continued to face and resolve various regulatory consent orders from OCC and CFPB stemming from the 2016 fake-accounts scandal and subsequent compliance failures. | 2024: Reports of tightened return-to-office enforcement including badge-swipe monitoring, generating employee pushback on Blind and Reddit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RECRUITING &amp; CONTACTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>Key Programs</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>CIB Summer Analyst, CIB Summer Associate, Technology Summer Internship, Wealth &amp; Investment Management Summer Internship, Commercial Banking Summer Internship, Operations/Corporate Functions Internship, Freshman/Sophomore Discovery Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>University Recruiting URL</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>https://www.wellsfargo.com/about/careers/early-careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>General Jobs URL</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>https://www.wellsfargo.com/about/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>LinkedIn Search Tip</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>Search LinkedIn for "Wells Fargo" + "Campus Recruiter" or "University Recruiting" or "Early Careers Talent Acquisition" filtered by current company to find division-specific campus recruiters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>Recruiter Tip</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>For IB roles, begin networking with Wells Fargo bankers on LinkedIn in the spring/summer before application season opens (July–August), attend every Wells Fargo campus event (attendance is tracked), and apply within the first two weeks of the portal opening. For non-target school candidates, securing a referral from a VP+ level employee is critical to getting past ATS screening. Employee referrals are submitted through an internal portal and carry moderate-to-significant weight — they move your resume past the initial screen but do not guarantee an interview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TECH STACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>Data / ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>DevTools / CI/CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>Notable OSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>Primary Languages</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERNSHIP PROGRAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>Program Exists (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>Program Name</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>CIB Summer Analyst, CIB Summer Associate, Technology Summer Internship, Wealth &amp; Investment Management Summer Internship, Commercial Banking Summer Internship, Operations/Corporate Functions Internship, Freshman/Sophomore Discovery Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>Duration (weeks)</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>10–12</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>Roles Available</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>Investment Banking Analyst/Associate, Markets, Research, Technology/Engineering, Cybersecurity, Data &amp; Analytics, Wealth Advisory, Commercial Banking, Risk, Compliance, Finance, HR, Marketing, Audit, Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>Weekly Comp (USD)</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>~$2,080–$2,200/wk (CIB IB front-office, annualized ~$110K at street rate); ~$1,520–$1,920/wk (Technology, varies by location — Charlotte/Chandler lower, SF/NYC higher); ~$1,120–$1,520/wk (Wealth &amp; Investment Management); ~$1,120–$1,400/wk (Commercial Banking); ~$1,000–$1,400/wk (Operations/Corporate Functions) — all verified from Glassdoor, Levels.fyi, and Wall Street Oasis intern salary reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>Return Offer Rate</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>~65–80% (CIB IB/Markets); ~60–75% (Technology); ~50–70% (Corporate functions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>Pipeline to Full-Time</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>The intern program is a central pipeline for full-time analyst and associate hiring, with a significant portion of full-time new-grad offers coming through intern conversions, reducing available external spots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>Application Timeline</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>CIB IB/Markets: July–August (apps open), offers as early as October–November; Technology: August–September (apps open), interviews October–January; Corporate functions: August–October (apps open), interviews November–February</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>Intern Headcount Est.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>Housing stipend or relocation assistance has been reported by some interns but is not universally guaranteed and appears to vary by location and year — candidates should confirm during the offer stage. No hard published GPA cutoff, but screening algorithms are believed to filter below 3.0 for most programs; CIB IB prefers 3.5+ (3.7+ competitive), Technology prefers 3.0+ (3.3+ competitive). Wells Fargo generally sponsors OPT/CPT for interns and H-1B for full-time conversions in eligible roles, though sponsorship availability varies by division. Applying to 2–3 programs maximum is advisable per anecdotal reports. Freshman/Sophomore Discovery Programs serve as pipeline/awareness programs for underrepresented candidates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WORKFORCE SIGNALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>WARN Activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>WARN Risk Level</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>WARN Analyst Note</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>Wells Fargo has been executing a multi-year headcount reduction strategy, having cut over 50,000 positions since 2020. While specific WARN filings were not detailed in the Step 1 research, the pattern of continuous layoffs across operations, technology, and corporate functions represents a sustained and material workforce reduction trend that candidates should weigh carefully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>Reddit / Glassdoor Themes</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>The most persistent and specific recurring themes are: (1) relentless layoffs and reorganizations creating a pervasive sense of job insecurity, with employees describing themselves as never feeling safe; (2) offshoring of technology and operations roles to India (Bangalore, Hyderabad) and the Philippines, directly threatening domestic positions; (3) a stark divide between the improving corporate/tech employee experience and the deteriorating branch/retail employee experience characterized by understaffing and aggressive metrics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>LinkedIn Signals</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>LinkedIn headcount direction is clearly declining, consistent with management's stated efficiency targets. Hiring activity appears concentrated in technology modernization, risk/compliance, and CIB growth areas, while operations, branch, and support functions continue to contract. Notable executive turnover has occurred as CEO Scharf brought in numerous external leaders from JPMorgan and other firms, creating an "us vs. them" dynamic with legacy employees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>News / Press Signals</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>Press coverage over the past 12 months has consistently covered Wells Fargo's ongoing headcount reductions (from ~227K to ~217K in 2024 alone), the continued Federal Reserve asset cap constraining growth, tightened return-to-office enforcement, and the company's multi-year efficiency initiative with CEO Scharf publicly stating that further position eliminations are planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>Overall Workforce Risk</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>Signal Confidence</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>Analyst Summary</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>Wells Fargo is financially healthy with ~$18.6B net income in FY2024, so headcount reductions are structural and efficiency-driven rather than distress-driven — the company is profitable but actively shrinking its workforce as a strategic choice. Roles most at risk include operations, back-office processing, branch/retail, and any function susceptible to offshoring or automation. Roles that are relatively safer include CIB front-office (where the bank is actively growing), technology modernization/AI/cloud, and risk/compliance (where regulatory demands create ongoing hiring need). For interns and entry-level candidates, the pipeline remains active and conversion rates are moderate-to-strong, but candidates should be aware that the overall organizational trajectory is contraction, meaning fewer permanent positions and greater competition for retention long-term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
